--- a/00_PROJECT_CONTROL/AUDIT_REGISTER.xlsx
+++ b/00_PROJECT_CONTROL/AUDIT_REGISTER.xlsx
@@ -413,23 +413,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Audit ID</t>
+          <t>Finding ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Finding</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -437,9 +437,26 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Action</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AUD-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Initial Import</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Imported 507 assets</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>

--- a/00_PROJECT_CONTROL/AUDIT_REGISTER.xlsx
+++ b/00_PROJECT_CONTROL/AUDIT_REGISTER.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AUDIT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,17 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>Finding</t>
         </is>
       </c>
     </row>
@@ -446,17 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Initial Import</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Imported 507 assets</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Initial classification pending for imported assets.</t>
         </is>
       </c>
     </row>
